--- a/artfynd/A 34968-2020 artfynd.xlsx
+++ b/artfynd/A 34968-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34968-2020 artfynd.xlsx
+++ b/artfynd/A 34968-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1561,6 +1561,123 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125101867</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100188</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Märsön, Vadholmsholm, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>617122</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6597498</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Aspö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ylva Linnman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ylva Linnman, Sari Roponen</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34968-2020 artfynd.xlsx
+++ b/artfynd/A 34968-2020 artfynd.xlsx
@@ -1566,7 +1566,7 @@
         <v>125101867</v>
       </c>
       <c r="B9" t="n">
-        <v>100188</v>
+        <v>100358</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 34968-2020 artfynd.xlsx
+++ b/artfynd/A 34968-2020 artfynd.xlsx
@@ -1566,12 +1566,7 @@
         <v>125101867</v>
       </c>
       <c r="B9" t="n">
-        <v>100358</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100413</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 34968-2020 artfynd.xlsx
+++ b/artfynd/A 34968-2020 artfynd.xlsx
@@ -1566,7 +1566,7 @@
         <v>125101867</v>
       </c>
       <c r="B9" t="n">
-        <v>100413</v>
+        <v>100420</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 34968-2020 artfynd.xlsx
+++ b/artfynd/A 34968-2020 artfynd.xlsx
@@ -1566,7 +1566,7 @@
         <v>125101867</v>
       </c>
       <c r="B9" t="n">
-        <v>100420</v>
+        <v>100423</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
